--- a/docs/perechen-otchetov/obrazcy/ФО-07.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-07.xlsx
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Начислено за период по кредиту = сумма начислений по строкам расчёта кредита (ФО-03) с датой в периоде.</t>
+          <t>Начислено за период по кредиту = сумма начислений по строкам расчёта кредита (вкладка «Расчёт» карточки кредита) с датой в периоде.</t>
         </is>
       </c>
     </row>

--- a/docs/perechen-otchetov/obrazcy/ФО-07.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-07.xlsx
@@ -589,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:O66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -791,34 +791,34 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>2780.37758</v>
+        <v>2793.91409</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>500.18563</v>
+        <v>537.2231399999999</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>200.91</v>
+        <v>239.0772</v>
       </c>
       <c r="G8" s="8" t="n">
         <v>112.5</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>3.7852</v>
+        <v>3.7619</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>2970.93841</v>
+        <v>2983.32193</v>
       </c>
       <c r="J8" s="8" t="n">
         <v>490.54791</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>88.6494</v>
+        <v>88.65947</v>
       </c>
       <c r="L8" s="8" t="n">
         <v>0</v>
@@ -827,7 +827,7 @@
         <v>38</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>0.65269</v>
+        <v>0.64262</v>
       </c>
       <c r="O8" s="8" t="n">
         <v>541.85</v>
@@ -2736,7 +2736,7 @@
         <v>869.56224</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>129.59663</v>
+        <v>129.70796</v>
       </c>
       <c r="F50" s="11" t="n">
         <v>24.035</v>
@@ -2745,16 +2745,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="11" t="n">
-        <v>3.13838</v>
+        <v>3.06817</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>978.26225</v>
+        <v>978.30337</v>
       </c>
       <c r="J50" s="11" t="n">
         <v>157.91536</v>
       </c>
       <c r="K50" s="11" t="n">
-        <v>25.24945</v>
+        <v>25.27113</v>
       </c>
       <c r="L50" s="11" t="n">
         <v>0</v>
@@ -2763,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="N50" s="11" t="n">
-        <v>0.58519</v>
+        <v>0.56351</v>
       </c>
       <c r="O50" s="11" t="n">
         <v>183.75</v>
@@ -2783,7 +2783,7 @@
         <v>519.25848</v>
       </c>
       <c r="E51" s="15" t="n">
-        <v>60.31085</v>
+        <v>60.36263</v>
       </c>
       <c r="F51" s="15" t="n">
         <v>0</v>
@@ -2792,7 +2792,7 @@
         <v>0</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>1.88655</v>
+        <v>1.83476</v>
       </c>
       <c r="I51" s="15" t="n">
         <v>581.45587</v>
@@ -2801,7 +2801,7 @@
         <v>66.08842</v>
       </c>
       <c r="K51" s="15" t="n">
-        <v>12.41361</v>
+        <v>12.42427</v>
       </c>
       <c r="L51" s="15" t="n">
         <v>0</v>
@@ -2810,7 +2810,7 @@
         <v>0</v>
       </c>
       <c r="N51" s="15" t="n">
-        <v>0.24797</v>
+        <v>0.23731</v>
       </c>
       <c r="O51" s="15" t="n">
         <v>78.75</v>
@@ -2828,7 +2828,7 @@
         <v>519.25848</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>60.31085</v>
+        <v>60.36263</v>
       </c>
       <c r="F52" s="18" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>1.88655</v>
+        <v>1.83476</v>
       </c>
       <c r="I52" s="18" t="n">
         <v>581.45587</v>
@@ -2846,7 +2846,7 @@
         <v>66.08842</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>12.41361</v>
+        <v>12.42427</v>
       </c>
       <c r="L52" s="18" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
         <v>0</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>0.24797</v>
+        <v>0.23731</v>
       </c>
       <c r="O52" s="18" t="n">
         <v>78.75</v>
@@ -2916,7 +2916,7 @@
         <v>330.5832</v>
       </c>
       <c r="E54" s="15" t="n">
-        <v>45.23314</v>
+        <v>45.27198</v>
       </c>
       <c r="F54" s="15" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>1.21241</v>
+        <v>1.17357</v>
       </c>
       <c r="I54" s="15" t="n">
         <v>377.02875</v>
@@ -2934,7 +2934,7 @@
         <v>91.82693999999999</v>
       </c>
       <c r="K54" s="15" t="n">
-        <v>12.83584</v>
+        <v>12.84686</v>
       </c>
       <c r="L54" s="15" t="n">
         <v>0</v>
@@ -2943,7 +2943,7 @@
         <v>0</v>
       </c>
       <c r="N54" s="15" t="n">
-        <v>0.33722</v>
+        <v>0.3262</v>
       </c>
       <c r="O54" s="15" t="n">
         <v>105</v>
@@ -2961,7 +2961,7 @@
         <v>330.5832</v>
       </c>
       <c r="E55" s="18" t="n">
-        <v>45.23314</v>
+        <v>45.27198</v>
       </c>
       <c r="F55" s="18" t="n">
         <v>0</v>
@@ -2970,7 +2970,7 @@
         <v>0</v>
       </c>
       <c r="H55" s="18" t="n">
-        <v>1.21241</v>
+        <v>1.17357</v>
       </c>
       <c r="I55" s="18" t="n">
         <v>377.02875</v>
@@ -2979,7 +2979,7 @@
         <v>91.82693999999999</v>
       </c>
       <c r="K55" s="18" t="n">
-        <v>12.83584</v>
+        <v>12.84686</v>
       </c>
       <c r="L55" s="18" t="n">
         <v>0</v>
@@ -2988,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="N55" s="18" t="n">
-        <v>0.33722</v>
+        <v>0.3262</v>
       </c>
       <c r="O55" s="18" t="n">
         <v>105</v>
@@ -3049,7 +3049,7 @@
         <v>19.72056</v>
       </c>
       <c r="E57" s="15" t="n">
-        <v>24.05264</v>
+        <v>24.07335</v>
       </c>
       <c r="F57" s="15" t="n">
         <v>24.035</v>
@@ -3058,10 +3058,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>0.03942</v>
+        <v>0.05984</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>19.77763</v>
+        <v>19.81875</v>
       </c>
       <c r="J57" s="15" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
         <v>19.72056</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>24.05264</v>
+        <v>24.07335</v>
       </c>
       <c r="F58" s="18" t="n">
         <v>24.035</v>
@@ -3103,10 +3103,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>0.03942</v>
+        <v>0.05984</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>19.77763</v>
+        <v>19.81875</v>
       </c>
       <c r="J58" s="18" t="n">
         <v>0</v>
@@ -3142,14 +3142,14 @@
         <v>0.27535</v>
       </c>
       <c r="F59" s="21" t="n">
-        <v>0.27547</v>
+        <v>0.275</v>
       </c>
       <c r="G59" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H59" s="20" t="n"/>
       <c r="I59" s="21" t="n">
-        <v>0.22603</v>
+        <v>0.2265</v>
       </c>
       <c r="J59" s="21" t="n">
         <v>0</v>
@@ -3175,34 +3175,34 @@
         </is>
       </c>
       <c r="B60" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D60" s="11" t="n">
-        <v>206.61474</v>
+        <v>220.15125</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>23.99198</v>
+        <v>60.91816</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>0</v>
+        <v>38.1672</v>
       </c>
       <c r="G60" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H60" s="11" t="n">
-        <v>0.64682</v>
+        <v>0.69372</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>231.25354</v>
+        <v>243.59594</v>
       </c>
       <c r="J60" s="11" t="n">
         <v>15.66968</v>
       </c>
       <c r="K60" s="11" t="n">
-        <v>14.71282</v>
+        <v>14.70121</v>
       </c>
       <c r="L60" s="11" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>0</v>
       </c>
       <c r="N60" s="11" t="n">
-        <v>0.0675</v>
+        <v>0.07911</v>
       </c>
       <c r="O60" s="11" t="n">
         <v>30.45</v>
@@ -3220,7 +3220,7 @@
     <row r="61" ht="13" customHeight="1">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t>ОсОО «Сулайман-Тоо Трейд»</t>
+          <t>ОсОО «Ала-Арча Энерго»</t>
         </is>
       </c>
       <c r="B61" s="13" t="n"/>
@@ -3228,28 +3228,28 @@
         <v>1</v>
       </c>
       <c r="D61" s="15" t="n">
-        <v>206.61474</v>
+        <v>13.53651</v>
       </c>
       <c r="E61" s="15" t="n">
-        <v>23.99198</v>
+        <v>36.94512</v>
       </c>
       <c r="F61" s="15" t="n">
-        <v>0</v>
+        <v>38.1672</v>
       </c>
       <c r="G61" s="15" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>0.64682</v>
+        <v>0.02797</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>231.25354</v>
+        <v>12.3424</v>
       </c>
       <c r="J61" s="15" t="n">
-        <v>15.66968</v>
+        <v>0</v>
       </c>
       <c r="K61" s="15" t="n">
-        <v>14.71282</v>
+        <v>0</v>
       </c>
       <c r="L61" s="15" t="n">
         <v>0</v>
@@ -3258,43 +3258,43 @@
         <v>0</v>
       </c>
       <c r="N61" s="15" t="n">
-        <v>0.0675</v>
+        <v>0</v>
       </c>
       <c r="O61" s="15" t="n">
-        <v>30.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" ht="13" customHeight="1">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>№ 21-1/207 от 15.11.2021, EUR</t>
+          <t>№ 21-9/040 от 20.09.2021, EUR</t>
         </is>
       </c>
       <c r="B62" s="17" t="n"/>
       <c r="C62" s="17" t="n"/>
       <c r="D62" s="18" t="n">
-        <v>206.61474</v>
+        <v>13.53651</v>
       </c>
       <c r="E62" s="18" t="n">
-        <v>23.99198</v>
+        <v>36.94512</v>
       </c>
       <c r="F62" s="18" t="n">
-        <v>0</v>
+        <v>38.1672</v>
       </c>
       <c r="G62" s="18" t="n">
         <v>0</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>0.64682</v>
+        <v>0.02797</v>
       </c>
       <c r="I62" s="18" t="n">
-        <v>231.25354</v>
+        <v>12.3424</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>15.66968</v>
+        <v>0</v>
       </c>
       <c r="K62" s="18" t="n">
-        <v>14.71282</v>
+        <v>0</v>
       </c>
       <c r="L62" s="18" t="n">
         <v>0</v>
@@ -3303,10 +3303,10 @@
         <v>0</v>
       </c>
       <c r="N62" s="18" t="n">
-        <v>0.0675</v>
+        <v>0</v>
       </c>
       <c r="O62" s="18" t="n">
-        <v>30.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" ht="13" customHeight="1">
@@ -3318,26 +3318,26 @@
       <c r="B63" s="20" t="n"/>
       <c r="C63" s="20" t="n"/>
       <c r="D63" s="21" t="n">
-        <v>2.04165</v>
+        <v>0.13376</v>
       </c>
       <c r="E63" s="21" t="n">
-        <v>0.23671</v>
+        <v>0.3648</v>
       </c>
       <c r="F63" s="21" t="n">
-        <v>0</v>
+        <v>0.37696</v>
       </c>
       <c r="G63" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="20" t="n"/>
       <c r="I63" s="21" t="n">
-        <v>2.27836</v>
+        <v>0.1216</v>
       </c>
       <c r="J63" s="21" t="n">
-        <v>0.15484</v>
+        <v>0</v>
       </c>
       <c r="K63" s="21" t="n">
-        <v>0.14516</v>
+        <v>0</v>
       </c>
       <c r="L63" s="21" t="n">
         <v>0</v>
@@ -3347,6 +3347,139 @@
       </c>
       <c r="N63" s="20" t="n"/>
       <c r="O63" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" ht="13" customHeight="1">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>ОсОО «Сулайман-Тоо Трейд»</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="n"/>
+      <c r="C64" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="15" t="n">
+        <v>206.61474</v>
+      </c>
+      <c r="E64" s="15" t="n">
+        <v>23.97304</v>
+      </c>
+      <c r="F64" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="15" t="n">
+        <v>0.66576</v>
+      </c>
+      <c r="I64" s="15" t="n">
+        <v>231.25354</v>
+      </c>
+      <c r="J64" s="15" t="n">
+        <v>15.66968</v>
+      </c>
+      <c r="K64" s="15" t="n">
+        <v>14.70121</v>
+      </c>
+      <c r="L64" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="15" t="n">
+        <v>0.07911</v>
+      </c>
+      <c r="O64" s="15" t="n">
+        <v>30.45</v>
+      </c>
+    </row>
+    <row r="65" ht="13" customHeight="1">
+      <c r="A65" s="16" t="inlineStr">
+        <is>
+          <t>№ 21-1/207 от 15.11.2021, EUR</t>
+        </is>
+      </c>
+      <c r="B65" s="17" t="n"/>
+      <c r="C65" s="17" t="n"/>
+      <c r="D65" s="18" t="n">
+        <v>206.61474</v>
+      </c>
+      <c r="E65" s="18" t="n">
+        <v>23.97304</v>
+      </c>
+      <c r="F65" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="18" t="n">
+        <v>0.66576</v>
+      </c>
+      <c r="I65" s="18" t="n">
+        <v>231.25354</v>
+      </c>
+      <c r="J65" s="18" t="n">
+        <v>15.66968</v>
+      </c>
+      <c r="K65" s="18" t="n">
+        <v>14.70121</v>
+      </c>
+      <c r="L65" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="18" t="n">
+        <v>0.07911</v>
+      </c>
+      <c r="O65" s="18" t="n">
+        <v>30.45</v>
+      </c>
+    </row>
+    <row r="66" ht="13" customHeight="1">
+      <c r="A66" s="19" t="inlineStr">
+        <is>
+          <t>в тыс. EUR (курс 101,20000 → 101,50000)</t>
+        </is>
+      </c>
+      <c r="B66" s="20" t="n"/>
+      <c r="C66" s="20" t="n"/>
+      <c r="D66" s="21" t="n">
+        <v>2.04165</v>
+      </c>
+      <c r="E66" s="21" t="n">
+        <v>0.23671</v>
+      </c>
+      <c r="F66" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="20" t="n"/>
+      <c r="I66" s="21" t="n">
+        <v>2.27836</v>
+      </c>
+      <c r="J66" s="21" t="n">
+        <v>0.15484</v>
+      </c>
+      <c r="K66" s="21" t="n">
+        <v>0.14516</v>
+      </c>
+      <c r="L66" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="20" t="n"/>
+      <c r="O66" s="21" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -3473,7 +3606,7 @@
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>на начало периода — на 31.08.2026: USD 87,20000, EUR 101,20000; на конец — на 30.09.2026: USD 87,50000, EUR 101,50000; начисление — по курсу каждого дня начисления, погашение и списание — по курсу дня операции</t>
+          <t>на начало периода — на 31.08.2026: USD 87,20000, EUR 101,20000; на конец — на 30.09.2026: USD 87,50000, EUR 101,50000; начисление — по курсу каждого дня начисления, погашение и списание — по курсу дня операции (05.09.2026 USD 87,40000, 21.09.2026 EUR 101,25000)</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4162,7 @@
       </c>
       <c r="B39" s="27" t="inlineStr">
         <is>
-          <t>Сентябрь 2026: заёмщиков 22, кредитов 25 (KGS — 19 и 21, USD — 3 и 3, EUR — 1 и 1). Проценты: на начало 2 780,378 + начислено 500,186 − погашено 200,910 − списано 112,500 + курсовая разница 3,785 = на конец 2 970,938. Штрафы: 490,548 + 88,649 − 0,000 − 38,000 + 0,653 = 541,850.</t>
+          <t>Сентябрь 2026: заёмщиков 23, кредитов 26 (KGS — 19 и 21, USD — 3 и 3, EUR — 2 и 2). Проценты: на начало 2 793,914 + начислено 537,223 − погашено 239,077 − списано 112,500 + курсовая разница 3,762 = на конец 2 983,322. Штрафы: 490,548 + 88,659 − 0,000 − 38,000 + 0,643 = 541,850.</t>
         </is>
       </c>
     </row>
@@ -4045,7 +4178,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="45" customHeight="1">
+    <row r="41" ht="60" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
           <t>3.</t>
@@ -4053,7 +4186,7 @@
       </c>
       <c r="B41" s="27" t="inlineStr">
         <is>
-          <t>Остатки на конец по каждому кредиту = ФО-02 на 01.10.2026 («по процентам», «по штрафам»): ИТОГО 2 970,938 и 541,850. Погашено = ФО-04 за сентябрь 2026: по процентам 200,910, по штрафам 0,000. Списано = ФО-11: КЗ-08 № 20-3/052 (списан 17.09.2026) — проценты 112,500, штрафы 38,000.</t>
+          <t>Остатки на конец по каждому кредиту = ФО-02 на 01.10.2026 («по процентам», «по штрафам»): ИТОГО 2 983,322 и 541,850 (= ФО-57). Погашено = ФО-04 за сентябрь 2026: по процентам 239,077 (в том числе КЗ-25 38,167), по штрафам 0,000. Списано = ФО-11: КЗ-08 № 20-3/052 (списан 17.09.2026) — проценты 112,500, штрафы 38,000.</t>
         </is>
       </c>
     </row>
@@ -4069,7 +4202,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="45" customHeight="1">
+    <row r="43" ht="60" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
           <t>5.</t>
@@ -4077,11 +4210,11 @@
       </c>
       <c r="B43" s="27" t="inlineStr">
         <is>
-          <t>Попадают: КЗ-15 (погашен 18.09.2026, на конец 0,000), КЗ-08 (списан 17.09.2026), КЗ-24 (только штрафы 18,400 на обоих концах, движения нет), КЗ-17 (выдан 15.09.2026). Не попадают: КЗ-18 (средства не получены) и КЗ-16 (погашен 20.03.2026, в сентябре ни остатка, ни движения).</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="60" customHeight="1">
+          <t>Попадают: КЗ-15 (погашен 18.09.2026, на конец 0,000), КЗ-08 (списан 17.09.2026), КЗ-24 (только штрафы 18,400 на обоих концах, движения нет), КЗ-17 (выдан 15.09.2026). Не попадают: КЗ-18 (средства не получены) и КЗ-16 (погашен 20.03.2026, в сентябре ни остатка, ни движения), КЗ-26 (не освоен — ни остатка, ни начислений).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="150" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
           <t>6.</t>
@@ -4089,7 +4222,7 @@
       </c>
       <c r="B44" s="27" t="inlineStr">
         <is>
-          <t>Валютные: на начало — курс 31.08.2026 (USD 87,20000, EUR 101,20000), на конец — 30.09.2026 (USD 87,50000, EUR 101,50000), начисление — по курсу каждого дня. КЗ-21 № 19-3/061: проценты 5,955 + 0,690 = 6,645 тыс. USD; в сомах 519,258 + 60,311 + курсовая разница 1,887 = 581,456. КЗ-11: платёж 05.09.2026 — 24,035 тыс. сом на проценты по курсу 87,25000.</t>
+          <t>Валютные: курсы НБКР из набора — 31.08.2026 (USD 87,20000, EUR 101,20000), 05.09.2026 (USD 87,40000), 21.09.2026 (EUR 101,25000), 30.09.2026 (USD 87,50000, EUR 101,50000); на начало — курс 31.08.2026, на конец — 30.09.2026, начисление — по курсу каждого дня. КЗ-21 № 19-3/061: проценты 5,955 + 0,690 = 6,645 тыс. USD; в сомах 519,258 + 60,363 + курсовая разница 1,835 = 581,456. КЗ-11: платёж 05.09.2026 — 275,00 USD процентов = 24,035 тыс. сом по курсу 87,40; проценты 0,22615 + 0,27535 − 0,27500 = 0,22650 тыс. USD, на конец 19,819 (= ФО-02, ФО-53, ФО-57). КЗ-25 № 21-9/040 (ставка 6,08 %, факт/360 — 12,16 EUR в день): на начало 133,76 EUR (11 дней с 21.08.2026) = 13,537; начислено 364,80 EUR (30 дней) = 36,945; погашено 21.09.2026 376,96 EUR = 38,167 по курсу 101,25, как поступили; на конец 121,60 EUR (10 дней с 21.09.2026) = 12,342; курсовая разница 0,028.</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4234,7 @@
       </c>
       <c r="B45" s="27" t="inlineStr">
         <is>
-          <t>КЗ-07 — под ОсОО «Ысык-Көл Логистик» (реквизиты на 30.09.2026, долг переведён 09.09.2026), одной строкой: 20,604 + 21,808 − 22,083 = 20,329. КЗ-21 «Кемин-Курулуш» — в KGS (два кредита) и в USD (№ 19-3/061).</t>
+          <t>КЗ-07 — под ОсОО «Ысык-Көл Логистик» (реквизиты на 30.09.2026, долг переведён 09.09.2026), одной строкой: 20,604 + 21,808 − 22,083 = 20,329. КЗ-21 «Кемин-Курулуш» — в KGS (два кредита) и в USD (№ 19-3/061); КЗ-25 «Ала-Арча Энерго» — в EUR перед «Сулайман-Тоо Трейд».</t>
         </is>
       </c>
     </row>
